--- a/fhir/CodeSystem-ehealth-consent-category.xlsx
+++ b/fhir/CodeSystem-ehealth-consent-category.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-consent-category.xlsx
+++ b/fhir/CodeSystem-ehealth-consent-category.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-consent-category.xlsx
+++ b/fhir/CodeSystem-ehealth-consent-category.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-consent-category.xlsx
+++ b/fhir/CodeSystem-ehealth-consent-category.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -175,10 +175,28 @@
     <t>Forward patient contact information to SSL provider</t>
   </si>
   <si>
+    <t>AFPA</t>
+  </si>
+  <si>
+    <t>Access for Parent Authority</t>
+  </si>
+  <si>
     <t>behavior-by-policy</t>
   </si>
   <si>
     <t>Behavior by policy</t>
+  </si>
+  <si>
+    <t>RPCTEOC</t>
+  </si>
+  <si>
+    <t>RelatedPerson Contributes to EpisodeOfCare</t>
+  </si>
+  <si>
+    <t>PORPI</t>
+  </si>
+  <si>
+    <t>Processing of RelatedPerson Information</t>
   </si>
 </sst>
 </file>
@@ -524,7 +542,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -597,6 +615,48 @@
         <v>54</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/fhir/CodeSystem-ehealth-consent-category.xlsx
+++ b/fhir/CodeSystem-ehealth-consent-category.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-consent-category.xlsx
+++ b/fhir/CodeSystem-ehealth-consent-category.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/CodeSystem-ehealth-consent-category.xlsx
+++ b/fhir/CodeSystem-ehealth-consent-category.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
